--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21880,7 +21880,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22430,7 +22430,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -22980,7 +22980,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -23926,7 +23926,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -25966,7 +25966,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27066,7 +27066,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21880,7 +21880,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22430,7 +22430,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -22980,7 +22980,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -23926,7 +23926,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -25966,7 +25966,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27066,7 +27066,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -28091,6 +28091,408 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28124,7 +28526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28609,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -28217,7 +28619,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -28237,7 +28639,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -1075,9 +1075,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1471,9 +1468,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1619,9 +1613,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1767,9 +1758,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2314,9 +2302,6 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2566,7 +2551,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -2864,9 +2849,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3116,7 +3098,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3414,9 +3396,6 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3666,7 +3645,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -3964,9 +3943,6 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4216,7 +4192,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4821,9 +4797,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5217,9 +5190,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5368,9 +5338,6 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5620,7 +5587,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -5767,9 +5734,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5915,9 +5879,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6462,9 +6423,6 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6714,7 +6672,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7012,9 +6970,6 @@
       <c r="P37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7264,7 +7219,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -7562,9 +7517,6 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7814,7 +7766,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8419,9 +8371,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8815,9 +8764,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8966,9 +8912,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9218,7 +9161,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9365,9 +9308,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9513,9 +9453,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10060,9 +9997,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10312,7 +10246,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10610,9 +10544,6 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10862,7 +10793,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -11160,9 +11091,6 @@
       <c r="P60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11412,7 +11340,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -11710,9 +11638,6 @@
       <c r="P63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11962,7 +11887,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -12109,9 +12034,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12419,9 +12341,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12815,9 +12734,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12963,9 +12879,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13111,9 +13024,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13658,9 +13568,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -13910,7 +13817,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -14208,9 +14115,6 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14460,7 +14364,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -14758,9 +14662,6 @@
       <c r="P80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15010,7 +14911,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -15308,9 +15209,6 @@
       <c r="P83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15560,7 +15458,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -15707,9 +15605,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16017,9 +15912,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -16413,9 +16305,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -16561,9 +16450,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16709,9 +16595,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17256,9 +17139,6 @@
       <c r="P94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17508,7 +17388,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -17806,9 +17686,6 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18058,7 +17935,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -18356,9 +18233,6 @@
       <c r="P100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -18608,7 +18482,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -18906,9 +18780,6 @@
       <c r="P103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -19158,7 +19029,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -19456,9 +19327,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19708,7 +19576,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -19855,9 +19723,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -20399,9 +20264,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -20795,9 +20657,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20943,9 +20802,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -21091,9 +20947,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -21487,9 +21340,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -21638,9 +21488,6 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -21890,7 +21737,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -22037,9 +21884,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -22188,9 +22032,6 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -22440,7 +22281,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -22587,9 +22428,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22738,9 +22576,6 @@
       <c r="P124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -22990,7 +22825,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -23137,9 +22972,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -23288,9 +23120,6 @@
       <c r="P127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -23540,7 +23369,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -23687,9 +23516,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -24083,9 +23909,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -24479,9 +24302,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -24627,9 +24447,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -25023,9 +24840,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -25174,9 +24988,6 @@
       <c r="P137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -25426,7 +25237,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -25573,9 +25384,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -25724,9 +25532,6 @@
       <c r="P140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -25976,7 +25781,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -26123,9 +25928,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -26274,9 +26076,6 @@
       <c r="P143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -26526,7 +26325,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -26673,9 +26472,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -26824,9 +26620,6 @@
       <c r="P146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -27076,7 +26869,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -27223,9 +27016,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -27619,9 +27409,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -28015,9 +27802,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -28166,9 +27950,6 @@
       <c r="P153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -28418,7 +28199,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN154" t="b">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -28274,6 +28274,405 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28307,7 +28706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -28390,7 +28789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -28400,7 +28799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -28420,7 +28819,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -19969,7 +19969,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23762,7 +23762,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -23865,12 +23865,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23904,95 +23904,84 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O131" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.002194047058651011</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24008,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -24068,98 +24057,23 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_172</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>German measles</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN132" t="b">
-        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -24253,17 +24167,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -24302,76 +24216,165 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24403,12 +24406,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -24455,82 +24458,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24546,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -24606,98 +24595,23 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Röda hund</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -24791,17 +24705,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -24826,7 +24740,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -24840,76 +24754,165 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Röda hund</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24944,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -24971,7 +24974,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -24985,9 +24988,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -24996,82 +24996,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25098,7 +25084,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -25150,98 +25136,23 @@
       <c r="P138" t="n">
         <v>0</v>
       </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -25335,17 +25246,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -25370,7 +25281,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -25384,76 +25295,168 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25485,12 +25488,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -25515,7 +25518,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -25524,98 +25527,81 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
-      </c>
-      <c r="P140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25642,7 +25628,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -25694,98 +25680,23 @@
       <c r="P141" t="n">
         <v>1</v>
       </c>
+      <c r="R141" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -25879,17 +25790,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -25914,7 +25825,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -25923,81 +25834,173 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26029,12 +26032,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -26059,7 +26062,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -26073,9 +26076,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -26084,82 +26084,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26186,7 +26172,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -26238,98 +26224,23 @@
       <c r="P144" t="n">
         <v>0</v>
       </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -26423,17 +26334,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -26458,7 +26369,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -26472,76 +26383,168 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26573,12 +26576,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -26603,7 +26606,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -26617,9 +26620,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -26628,82 +26628,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26730,7 +26716,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -26782,98 +26768,23 @@
       <c r="P147" t="n">
         <v>0</v>
       </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -26967,17 +26878,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -27002,12 +26913,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N148" t="n">
@@ -27016,27 +26927,105 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P148" t="n">
+        <v>0</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
@@ -27046,12 +27035,12 @@
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -27059,47 +27048,47 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27126,7 +27115,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -27175,98 +27164,23 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>SER_AU_RUBELLA</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>SER_AU_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
-        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -27360,17 +27274,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -27409,17 +27323,34 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -27427,9 +27358,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>1</v>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
@@ -27439,12 +27428,12 @@
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -27452,47 +27441,47 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27519,7 +27508,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -27568,98 +27557,23 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_172</t>
         </is>
       </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>German measles</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -27753,17 +27667,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -27802,76 +27716,165 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27903,12 +27906,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -27933,7 +27936,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -27947,9 +27950,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="P153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -27958,82 +27958,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28060,7 +28046,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -28112,98 +28098,23 @@
       <c r="P154" t="n">
         <v>0</v>
       </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -28297,7 +28208,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -28332,7 +28243,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -28349,23 +28260,98 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U155" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
@@ -28459,7 +28445,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -28511,98 +28497,23 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -28668,6 +28579,243 @@
         </is>
       </c>
       <c r="BC156" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -28789,7 +28937,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -28799,7 +28947,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -28851,7 +28999,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>244</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -28821,6 +28821,405 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28854,7 +29253,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -28937,7 +29336,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -28947,7 +29346,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -28967,7 +29366,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -2541,7 +2541,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19870,7 +19870,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25958,7 +25958,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30395,7 +30395,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31333,7 +31333,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32271,7 +32271,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33209,7 +33209,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -33996,7 +33996,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -36557,7 +36557,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -37495,7 +37495,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -38433,7 +38433,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -39220,7 +39220,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -40157,7 +40157,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40950,7 +40950,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -41743,7 +41743,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -2541,7 +2541,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19870,7 +19870,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25958,7 +25958,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30395,7 +30395,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31333,7 +31333,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32271,7 +32271,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33209,7 +33209,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -33996,7 +33996,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -36557,7 +36557,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -37495,7 +37495,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -38433,7 +38433,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -39220,7 +39220,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -40157,7 +40157,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40950,7 +40950,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -41743,7 +41743,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -34650,12 +34650,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -34728,42 +34728,42 @@
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34795,12 +34795,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -34847,82 +34847,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34949,7 +34935,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -34998,98 +34984,23 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Röda hund</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN188" t="b">
-        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -35183,17 +35094,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -35218,7 +35129,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -35232,76 +35143,165 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Röda hund</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35333,12 +35333,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35363,7 +35363,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -35377,9 +35377,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -35388,82 +35385,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35473,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -35542,98 +35525,23 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -35727,17 +35635,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35779,12 +35687,34 @@
       <c r="P192" t="n">
         <v>0</v>
       </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -35792,6 +35722,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35799,7 +35787,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
@@ -35809,55 +35797,55 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35884,7 +35872,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -35936,98 +35924,18 @@
       <c r="P193" t="n">
         <v>0</v>
       </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -36121,17 +36029,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -36156,7 +36064,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -36170,76 +36078,168 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="R194" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36271,12 +36271,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -36301,7 +36301,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -36310,98 +36310,81 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>1</v>
-      </c>
-      <c r="P195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36428,7 +36411,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -36480,98 +36463,23 @@
       <c r="P196" t="n">
         <v>1</v>
       </c>
+      <c r="R196" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -36665,17 +36573,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36709,20 +36617,42 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
-      </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -36730,6 +36660,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36737,7 +36725,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -36747,55 +36735,55 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36822,7 +36810,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -36874,98 +36862,18 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -37059,17 +36967,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -37094,7 +37002,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -37108,76 +37016,168 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37209,12 +37209,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -37239,7 +37239,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -37253,9 +37253,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -37264,82 +37261,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37366,7 +37349,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -37418,98 +37401,23 @@
       <c r="P201" t="n">
         <v>0</v>
       </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -37603,17 +37511,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37655,12 +37563,34 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -37668,6 +37598,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37675,7 +37663,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
@@ -37685,55 +37673,55 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37760,7 +37748,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -37812,98 +37800,18 @@
       <c r="P203" t="n">
         <v>0</v>
       </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -37997,17 +37905,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -38032,7 +37940,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -38046,76 +37954,168 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="R204" t="n">
-        <v>0</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38147,12 +38147,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -38177,7 +38177,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -38191,9 +38191,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="P205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -38202,82 +38199,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38304,7 +38287,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -38356,98 +38339,23 @@
       <c r="P206" t="n">
         <v>0</v>
       </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U206" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -38541,17 +38449,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38593,12 +38501,34 @@
       <c r="P207" t="n">
         <v>0</v>
       </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -38606,6 +38536,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38613,7 +38601,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
@@ -38623,55 +38611,55 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38698,7 +38686,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -38750,98 +38738,18 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -38935,17 +38843,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38970,12 +38878,12 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -38984,90 +38892,168 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P209" t="n">
+        <v>0</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39094,7 +39080,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -39143,98 +39129,23 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U210" t="inlineStr">
         <is>
           <t>SER_AU_RUBELLA</t>
         </is>
       </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_AU_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -39328,17 +39239,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -39377,17 +39288,34 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -39395,9 +39323,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
@@ -39407,12 +39393,12 @@
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AT211" t="n">
@@ -39420,47 +39406,47 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39487,7 +39473,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -39536,98 +39522,23 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U212" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_172</t>
         </is>
       </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>German measles</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -39721,17 +39632,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39770,76 +39681,165 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39871,12 +39871,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -39901,7 +39901,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -39915,9 +39915,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="P214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -39926,82 +39923,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ214" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40028,7 +40011,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -40080,98 +40063,23 @@
       <c r="P215" t="n">
         <v>0</v>
       </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U215" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN215" t="b">
-        <v>1</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
@@ -40265,17 +40173,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -40317,12 +40225,34 @@
       <c r="P216" t="n">
         <v>0</v>
       </c>
-      <c r="R216" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -40330,6 +40260,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN216" t="b">
+        <v>1</v>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40337,7 +40325,7 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
@@ -40347,55 +40335,55 @@
       </c>
       <c r="AS216" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40422,7 +40410,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -40474,98 +40462,18 @@
       <c r="P217" t="n">
         <v>0</v>
       </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -40659,17 +40567,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -40694,7 +40602,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -40711,17 +40619,34 @@
       <c r="P218" t="n">
         <v>0</v>
       </c>
-      <c r="R218" t="n">
-        <v>0</v>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -40729,6 +40654,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
+        <v>1</v>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40736,7 +40719,7 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
@@ -40746,55 +40729,55 @@
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40821,7 +40804,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -40873,98 +40856,23 @@
       <c r="P219" t="n">
         <v>0</v>
       </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U219" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN219" t="b">
-        <v>1</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
@@ -41058,17 +40966,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -41110,12 +41018,34 @@
       <c r="P220" t="n">
         <v>0</v>
       </c>
-      <c r="R220" t="n">
-        <v>0</v>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -41123,6 +41053,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN220" t="b">
+        <v>1</v>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -41130,7 +41118,7 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
@@ -41140,55 +41128,55 @@
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41215,7 +41203,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -41267,98 +41255,18 @@
       <c r="P221" t="n">
         <v>0</v>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN221" t="b">
-        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -41452,17 +41360,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -41487,7 +41395,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -41504,17 +41412,34 @@
       <c r="P222" t="n">
         <v>0</v>
       </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -41522,6 +41447,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -41529,7 +41512,7 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
@@ -41539,55 +41522,55 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41614,7 +41597,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -41666,98 +41649,23 @@
       <c r="P223" t="n">
         <v>0</v>
       </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U223" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG223" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM223" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN223" t="b">
-        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
@@ -41851,17 +41759,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -41903,12 +41811,34 @@
       <c r="P224" t="n">
         <v>0</v>
       </c>
-      <c r="R224" t="n">
-        <v>0</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -41916,6 +41846,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>1</v>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -41923,7 +41911,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
@@ -41933,55 +41921,55 @@
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42008,7 +41996,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -42060,98 +42048,18 @@
       <c r="P225" t="n">
         <v>0</v>
       </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
@@ -42217,6 +42125,243 @@
         </is>
       </c>
       <c r="BC225" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -42338,7 +42483,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -42348,7 +42493,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
